--- a/Team-Data/2007-08/3-3-2007-08.xlsx
+++ b/Team-Data/2007-08/3-3-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>21</v>
@@ -954,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
         <v>8</v>
@@ -984,7 +1051,7 @@
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
@@ -1130,7 +1197,7 @@
         <v>17</v>
       </c>
       <c r="AM4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN4" t="n">
         <v>15</v>
@@ -1139,7 +1206,7 @@
         <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
         <v>29</v>
@@ -1148,7 +1215,7 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
         <v>25</v>
@@ -1172,7 +1239,7 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>22</v>
@@ -1354,10 +1421,10 @@
         <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1497,7 +1564,7 @@
         <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>0.639</v>
+        <v>0.65</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1589,25 +1656,25 @@
         <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>0.461</v>
       </c>
       <c r="L7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M7" t="n">
         <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P7" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0.8179999999999999</v>
@@ -1616,22 +1683,22 @@
         <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V7" t="n">
         <v>12.9</v>
       </c>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y7" t="n">
         <v>4.2</v>
@@ -1640,19 +1707,19 @@
         <v>21.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
         <v>8</v>
@@ -1661,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>16</v>
@@ -1670,7 +1737,7 @@
         <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
@@ -1679,13 +1746,13 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1700,7 +1767,7 @@
         <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,22 +1776,22 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB7" t="n">
         <v>13</v>
       </c>
-      <c r="BB7" t="n">
-        <v>12</v>
-      </c>
       <c r="BC7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>8.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2034,7 +2101,7 @@
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2228,7 +2295,7 @@
         <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -2416,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
         <v>11</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="n">
         <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,10 +2748,10 @@
         <v>34.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.5</v>
+        <v>78.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
         <v>4.2</v>
@@ -2693,28 +2760,28 @@
         <v>12.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O13" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P13" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="Q13" t="n">
         <v>0.788</v>
       </c>
       <c r="R13" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S13" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T13" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="U13" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
         <v>14.4</v>
@@ -2729,25 +2796,25 @@
         <v>5.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-5.5</v>
+        <v>-5.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2786,13 +2853,13 @@
         <v>28</v>
       </c>
       <c r="AS13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AU13" t="n">
         <v>16</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>15</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2801,19 +2868,19 @@
         <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
         <v>12</v>
       </c>
       <c r="BB13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC13" t="n">
         <v>23</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3177,10 +3244,10 @@
         <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>21</v>
@@ -3359,7 +3426,7 @@
         <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
         <v>23</v>
@@ -3538,10 +3605,10 @@
         <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC17" t="n">
         <v>27</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3669,7 +3736,7 @@
         <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
         <v>19</v>
       </c>
       <c r="G20" t="n">
-        <v>0.678</v>
+        <v>0.672</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
@@ -3955,52 +4022,52 @@
         <v>38.3</v>
       </c>
       <c r="J20" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L20" t="n">
         <v>7.8</v>
       </c>
       <c r="M20" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N20" t="n">
         <v>0.389</v>
       </c>
       <c r="O20" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P20" t="n">
         <v>20.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T20" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
       </c>
       <c r="V20" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
         <v>3.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z20" t="n">
         <v>19</v>
@@ -4012,10 +4079,10 @@
         <v>100</v>
       </c>
       <c r="AC20" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4027,16 +4094,16 @@
         <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK20" t="n">
         <v>7</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>6</v>
@@ -4060,13 +4127,13 @@
         <v>15</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4078,7 +4145,7 @@
         <v>28</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
         <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0.305</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
@@ -4137,10 +4204,10 @@
         <v>35.2</v>
       </c>
       <c r="J21" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
         <v>5.8</v>
@@ -4149,40 +4216,40 @@
         <v>17.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O21" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="R21" t="n">
         <v>12.2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U21" t="n">
         <v>18.6</v>
       </c>
       <c r="V21" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W21" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X21" t="n">
         <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
         <v>21.3</v>
@@ -4191,13 +4258,13 @@
         <v>21.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.2</v>
+        <v>-6.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4224,25 +4291,25 @@
         <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN21" t="n">
         <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
         <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR21" t="n">
         <v>9</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
         <v>16</v>
@@ -4254,7 +4321,7 @@
         <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,13 +4333,13 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB21" t="n">
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF22" t="n">
         <v>11</v>
@@ -4427,7 +4494,7 @@
         <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
         <v>24</v>
@@ -4442,7 +4509,7 @@
         <v>24</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
         <v>15</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -4483,58 +4550,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F23" t="n">
         <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.459</v>
+        <v>0.45</v>
       </c>
       <c r="H23" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J23" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M23" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.318</v>
+        <v>0.314</v>
       </c>
       <c r="O23" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P23" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.702</v>
+        <v>0.703</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S23" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="T23" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V23" t="n">
         <v>15.1</v>
@@ -4549,19 +4616,19 @@
         <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>17</v>
@@ -4570,10 +4637,10 @@
         <v>18</v>
       </c>
       <c r="AG23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4597,7 +4664,7 @@
         <v>20</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4609,10 +4676,10 @@
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
@@ -4621,19 +4688,19 @@
         <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4970,7 +5037,7 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
@@ -4991,7 +5058,7 @@
         <v>2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF26" t="n">
         <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH26" t="n">
         <v>18</v>
@@ -5152,10 +5219,10 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>4</v>
@@ -5301,7 +5368,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5698,7 +5765,7 @@
         <v>26</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT29" t="n">
         <v>26</v>
@@ -5719,7 +5786,7 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -5757,94 +5824,94 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F30" t="n">
         <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.639</v>
+        <v>0.633</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.494</v>
+        <v>0.493</v>
       </c>
       <c r="L30" t="n">
         <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="O30" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="P30" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.758</v>
+        <v>0.755</v>
       </c>
       <c r="R30" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T30" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W30" t="n">
         <v>9</v>
       </c>
       <c r="X30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AA30" t="n">
         <v>23.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.5</v>
+        <v>105.4</v>
       </c>
       <c r="AC30" t="n">
         <v>5.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5874,13 +5941,13 @@
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6065,7 +6132,7 @@
         <v>24</v>
       </c>
       <c r="AT31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
@@ -6080,7 +6147,7 @@
         <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>3</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-3-2007-08</t>
+          <t>2008-03-03</t>
         </is>
       </c>
     </row>
